--- a/Diseño vida y ministerio cristiano.xlsx
+++ b/Diseño vida y ministerio cristiano.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23901"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Reunion\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SmlB\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A55B2E7A-93F6-4CC9-908F-A121796F00D4}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44C3C55C-A069-4DF2-A3A8-35F8D194A16D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{BBC1ECDB-C94F-43B9-A03C-69C957DE57B4}"/>
+    <workbookView xWindow="-120" yWindow="255" windowWidth="29040" windowHeight="17865" xr2:uid="{BBC1ECDB-C94F-43B9-A03C-69C957DE57B4}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -400,22 +400,13 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -427,10 +418,19 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1725,22 +1725,22 @@
   </cols>
   <sheetData>
     <row r="5" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="16"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="17" t="s">
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="H5" s="18"/>
-      <c r="I5" s="18"/>
-      <c r="J5" s="18"/>
-      <c r="K5" s="18"/>
-      <c r="L5" s="18"/>
+      <c r="H5" s="15"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="15"/>
+      <c r="K5" s="15"/>
+      <c r="L5" s="15"/>
     </row>
     <row r="6" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
@@ -1748,27 +1748,27 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
       <c r="G6" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
     </row>
     <row r="7" spans="1:12" ht="18" x14ac:dyDescent="0.25">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
       <c r="G7" s="4" t="s">
         <v>7</v>
       </c>
@@ -1779,14 +1779,14 @@
       <c r="L7" s="4"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="13"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
       <c r="G8" s="3" t="s">
         <v>15</v>
       </c>
@@ -1836,11 +1836,11 @@
       <c r="A11" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
       <c r="G11" s="4" t="s">
         <v>7</v>
       </c>
@@ -1854,11 +1854,11 @@
       <c r="A12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B12" s="12"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
       <c r="G12" s="3" t="s">
         <v>18</v>
       </c>
@@ -2051,22 +2051,22 @@
       <c r="L22" s="4"/>
     </row>
     <row r="23" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="19" t="s">
+      <c r="A23" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="B23" s="16"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="17" t="s">
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="H23" s="18"/>
-      <c r="I23" s="18"/>
-      <c r="J23" s="18"/>
-      <c r="K23" s="18"/>
-      <c r="L23" s="18"/>
+      <c r="H23" s="15"/>
+      <c r="I23" s="15"/>
+      <c r="J23" s="15"/>
+      <c r="K23" s="15"/>
+      <c r="L23" s="15"/>
     </row>
     <row r="24" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
@@ -2074,27 +2074,27 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="16"/>
       <c r="G24" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H24" s="12"/>
-      <c r="I24" s="12"/>
-      <c r="J24" s="12"/>
-      <c r="K24" s="12"/>
-      <c r="L24" s="12"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11"/>
+      <c r="J24" s="11"/>
+      <c r="K24" s="11"/>
+      <c r="L24" s="11"/>
     </row>
     <row r="25" spans="1:12" ht="18" x14ac:dyDescent="0.25">
-      <c r="A25" s="14" t="s">
+      <c r="A25" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
+      <c r="B25" s="17"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="17"/>
       <c r="G25" s="4" t="s">
         <v>7</v>
       </c>
@@ -2105,14 +2105,14 @@
       <c r="L25" s="4"/>
     </row>
     <row r="26" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="20" t="s">
+      <c r="A26" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="B26" s="20"/>
-      <c r="C26" s="20"/>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="20"/>
+      <c r="B26" s="18"/>
+      <c r="C26" s="18"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
       <c r="G26" s="3" t="s">
         <v>15</v>
       </c>
@@ -2162,11 +2162,11 @@
       <c r="A29" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B29" s="11"/>
-      <c r="C29" s="11"/>
-      <c r="D29" s="11"/>
-      <c r="E29" s="11"/>
-      <c r="F29" s="11"/>
+      <c r="B29" s="10"/>
+      <c r="C29" s="10"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="10"/>
+      <c r="F29" s="10"/>
       <c r="G29" s="4" t="s">
         <v>7</v>
       </c>
@@ -2180,11 +2180,11 @@
       <c r="A30" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B30" s="12"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
       <c r="G30" s="3" t="s">
         <v>23</v>
       </c>
@@ -2377,22 +2377,22 @@
       <c r="L40" s="4"/>
     </row>
     <row r="48" spans="1:12" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A48" s="19" t="s">
+      <c r="A48" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="B48" s="16"/>
-      <c r="C48" s="16"/>
-      <c r="D48" s="16"/>
-      <c r="E48" s="16"/>
-      <c r="F48" s="16"/>
-      <c r="G48" s="17" t="s">
+      <c r="B48" s="13"/>
+      <c r="C48" s="13"/>
+      <c r="D48" s="13"/>
+      <c r="E48" s="13"/>
+      <c r="F48" s="13"/>
+      <c r="G48" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="H48" s="18"/>
-      <c r="I48" s="18"/>
-      <c r="J48" s="18"/>
-      <c r="K48" s="18"/>
-      <c r="L48" s="18"/>
+      <c r="H48" s="15"/>
+      <c r="I48" s="15"/>
+      <c r="J48" s="15"/>
+      <c r="K48" s="15"/>
+      <c r="L48" s="15"/>
     </row>
     <row r="49" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
@@ -2400,27 +2400,27 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
-      <c r="D49" s="13"/>
-      <c r="E49" s="13"/>
-      <c r="F49" s="13"/>
+      <c r="D49" s="16"/>
+      <c r="E49" s="16"/>
+      <c r="F49" s="16"/>
       <c r="G49" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H49" s="12"/>
-      <c r="I49" s="12"/>
-      <c r="J49" s="12"/>
-      <c r="K49" s="12"/>
-      <c r="L49" s="12"/>
+      <c r="H49" s="11"/>
+      <c r="I49" s="11"/>
+      <c r="J49" s="11"/>
+      <c r="K49" s="11"/>
+      <c r="L49" s="11"/>
     </row>
     <row r="50" spans="1:12" ht="18" x14ac:dyDescent="0.25">
-      <c r="A50" s="14" t="s">
+      <c r="A50" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="B50" s="14"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
+      <c r="B50" s="17"/>
+      <c r="C50" s="17"/>
+      <c r="D50" s="17"/>
+      <c r="E50" s="17"/>
+      <c r="F50" s="17"/>
       <c r="G50" s="4" t="s">
         <v>7</v>
       </c>
@@ -2488,11 +2488,11 @@
       <c r="A54" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B54" s="11"/>
-      <c r="C54" s="11"/>
-      <c r="D54" s="11"/>
-      <c r="E54" s="11"/>
-      <c r="F54" s="11"/>
+      <c r="B54" s="10"/>
+      <c r="C54" s="10"/>
+      <c r="D54" s="10"/>
+      <c r="E54" s="10"/>
+      <c r="F54" s="10"/>
       <c r="G54" s="4" t="s">
         <v>7</v>
       </c>
@@ -2506,11 +2506,11 @@
       <c r="A55" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B55" s="12"/>
-      <c r="C55" s="12"/>
-      <c r="D55" s="12"/>
-      <c r="E55" s="12"/>
-      <c r="F55" s="12"/>
+      <c r="B55" s="11"/>
+      <c r="C55" s="11"/>
+      <c r="D55" s="11"/>
+      <c r="E55" s="11"/>
+      <c r="F55" s="11"/>
       <c r="G55" s="3" t="s">
         <v>27</v>
       </c>
@@ -2703,22 +2703,22 @@
       <c r="L65" s="4"/>
     </row>
     <row r="66" spans="1:12" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A66" s="15" t="s">
+      <c r="A66" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="B66" s="16"/>
-      <c r="C66" s="16"/>
-      <c r="D66" s="16"/>
-      <c r="E66" s="16"/>
-      <c r="F66" s="16"/>
-      <c r="G66" s="17" t="s">
+      <c r="B66" s="13"/>
+      <c r="C66" s="13"/>
+      <c r="D66" s="13"/>
+      <c r="E66" s="13"/>
+      <c r="F66" s="13"/>
+      <c r="G66" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="H66" s="18"/>
-      <c r="I66" s="18"/>
-      <c r="J66" s="18"/>
-      <c r="K66" s="18"/>
-      <c r="L66" s="18"/>
+      <c r="H66" s="15"/>
+      <c r="I66" s="15"/>
+      <c r="J66" s="15"/>
+      <c r="K66" s="15"/>
+      <c r="L66" s="15"/>
     </row>
     <row r="67" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
@@ -2726,27 +2726,27 @@
       </c>
       <c r="B67" s="5"/>
       <c r="C67" s="5"/>
-      <c r="D67" s="13"/>
-      <c r="E67" s="13"/>
-      <c r="F67" s="13"/>
+      <c r="D67" s="16"/>
+      <c r="E67" s="16"/>
+      <c r="F67" s="16"/>
       <c r="G67" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H67" s="12"/>
-      <c r="I67" s="12"/>
-      <c r="J67" s="12"/>
-      <c r="K67" s="12"/>
-      <c r="L67" s="12"/>
+      <c r="H67" s="11"/>
+      <c r="I67" s="11"/>
+      <c r="J67" s="11"/>
+      <c r="K67" s="11"/>
+      <c r="L67" s="11"/>
     </row>
     <row r="68" spans="1:12" ht="18" x14ac:dyDescent="0.25">
-      <c r="A68" s="14" t="s">
+      <c r="A68" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="B68" s="14"/>
-      <c r="C68" s="14"/>
-      <c r="D68" s="14"/>
-      <c r="E68" s="14"/>
-      <c r="F68" s="14"/>
+      <c r="B68" s="17"/>
+      <c r="C68" s="17"/>
+      <c r="D68" s="17"/>
+      <c r="E68" s="17"/>
+      <c r="F68" s="17"/>
       <c r="G68" s="4" t="s">
         <v>7</v>
       </c>
@@ -2814,11 +2814,11 @@
       <c r="A72" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B72" s="11"/>
-      <c r="C72" s="11"/>
-      <c r="D72" s="11"/>
-      <c r="E72" s="11"/>
-      <c r="F72" s="11"/>
+      <c r="B72" s="10"/>
+      <c r="C72" s="10"/>
+      <c r="D72" s="10"/>
+      <c r="E72" s="10"/>
+      <c r="F72" s="10"/>
       <c r="G72" s="4" t="s">
         <v>7</v>
       </c>
@@ -2832,11 +2832,11 @@
       <c r="A73" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B73" s="12"/>
-      <c r="C73" s="12"/>
-      <c r="D73" s="12"/>
-      <c r="E73" s="12"/>
-      <c r="F73" s="12"/>
+      <c r="B73" s="11"/>
+      <c r="C73" s="11"/>
+      <c r="D73" s="11"/>
+      <c r="E73" s="11"/>
+      <c r="F73" s="11"/>
       <c r="G73" s="3" t="s">
         <v>30</v>
       </c>
@@ -2910,11 +2910,11 @@
       <c r="E77" s="4"/>
       <c r="F77" s="4"/>
       <c r="G77" s="3"/>
-      <c r="H77" s="10"/>
-      <c r="I77" s="10"/>
-      <c r="J77" s="10"/>
-      <c r="K77" s="10"/>
-      <c r="L77" s="10"/>
+      <c r="H77" s="20"/>
+      <c r="I77" s="20"/>
+      <c r="J77" s="20"/>
+      <c r="K77" s="20"/>
+      <c r="L77" s="20"/>
     </row>
     <row r="78" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
@@ -3030,45 +3030,99 @@
     </row>
   </sheetData>
   <mergeCells count="156">
-    <mergeCell ref="A39:F39"/>
-    <mergeCell ref="A40:F40"/>
-    <mergeCell ref="G39:L39"/>
-    <mergeCell ref="G40:L40"/>
-    <mergeCell ref="A37:F37"/>
-    <mergeCell ref="A38:F38"/>
-    <mergeCell ref="I37:L37"/>
-    <mergeCell ref="G38:I38"/>
-    <mergeCell ref="J38:L38"/>
-    <mergeCell ref="A32:F32"/>
-    <mergeCell ref="G32:L32"/>
-    <mergeCell ref="A33:F33"/>
-    <mergeCell ref="G33:L33"/>
-    <mergeCell ref="A34:F34"/>
-    <mergeCell ref="G34:L34"/>
-    <mergeCell ref="A35:F35"/>
-    <mergeCell ref="G35:L35"/>
-    <mergeCell ref="A36:F36"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="I36:L36"/>
-    <mergeCell ref="A27:F27"/>
-    <mergeCell ref="G27:L27"/>
-    <mergeCell ref="A28:F28"/>
-    <mergeCell ref="G28:L28"/>
-    <mergeCell ref="A29:F29"/>
-    <mergeCell ref="G29:L29"/>
-    <mergeCell ref="A30:F30"/>
-    <mergeCell ref="G30:L30"/>
-    <mergeCell ref="A31:F31"/>
-    <mergeCell ref="G31:L31"/>
-    <mergeCell ref="A23:F23"/>
-    <mergeCell ref="G23:L23"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="G24:L24"/>
-    <mergeCell ref="A25:F25"/>
-    <mergeCell ref="G25:L25"/>
-    <mergeCell ref="A26:F26"/>
-    <mergeCell ref="G26:L26"/>
+    <mergeCell ref="A82:F82"/>
+    <mergeCell ref="G82:L82"/>
+    <mergeCell ref="A83:F83"/>
+    <mergeCell ref="G83:L83"/>
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="I80:L80"/>
+    <mergeCell ref="A81:F81"/>
+    <mergeCell ref="G81:I81"/>
+    <mergeCell ref="J81:L81"/>
+    <mergeCell ref="A78:F78"/>
+    <mergeCell ref="A79:F79"/>
+    <mergeCell ref="G79:H79"/>
+    <mergeCell ref="I79:L79"/>
+    <mergeCell ref="A75:F75"/>
+    <mergeCell ref="G75:L75"/>
+    <mergeCell ref="A76:F76"/>
+    <mergeCell ref="G76:L76"/>
+    <mergeCell ref="A77:F77"/>
+    <mergeCell ref="G78:L78"/>
+    <mergeCell ref="G77:L77"/>
+    <mergeCell ref="A72:F72"/>
+    <mergeCell ref="G72:L72"/>
+    <mergeCell ref="A73:F73"/>
+    <mergeCell ref="G73:L73"/>
+    <mergeCell ref="A74:F74"/>
+    <mergeCell ref="G74:L74"/>
+    <mergeCell ref="A69:F69"/>
+    <mergeCell ref="G69:L69"/>
+    <mergeCell ref="A70:F70"/>
+    <mergeCell ref="G70:L70"/>
+    <mergeCell ref="A71:F71"/>
+    <mergeCell ref="G71:L71"/>
+    <mergeCell ref="A67:C67"/>
+    <mergeCell ref="D67:F67"/>
+    <mergeCell ref="G67:L67"/>
+    <mergeCell ref="A68:F68"/>
+    <mergeCell ref="G68:L68"/>
+    <mergeCell ref="A64:F64"/>
+    <mergeCell ref="G64:L64"/>
+    <mergeCell ref="A65:F65"/>
+    <mergeCell ref="G65:L65"/>
+    <mergeCell ref="A66:F66"/>
+    <mergeCell ref="G66:L66"/>
+    <mergeCell ref="A62:F62"/>
+    <mergeCell ref="I62:L62"/>
+    <mergeCell ref="A63:F63"/>
+    <mergeCell ref="G63:I63"/>
+    <mergeCell ref="J63:L63"/>
+    <mergeCell ref="A59:F59"/>
+    <mergeCell ref="G59:L59"/>
+    <mergeCell ref="A60:F60"/>
+    <mergeCell ref="G60:L60"/>
+    <mergeCell ref="A61:F61"/>
+    <mergeCell ref="G61:H61"/>
+    <mergeCell ref="I61:L61"/>
+    <mergeCell ref="A56:F56"/>
+    <mergeCell ref="G56:L56"/>
+    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="G57:L57"/>
+    <mergeCell ref="A58:F58"/>
+    <mergeCell ref="G58:L58"/>
+    <mergeCell ref="A53:F53"/>
+    <mergeCell ref="G53:L53"/>
+    <mergeCell ref="A54:F54"/>
+    <mergeCell ref="G54:L54"/>
+    <mergeCell ref="A55:F55"/>
+    <mergeCell ref="G55:L55"/>
+    <mergeCell ref="A50:F50"/>
+    <mergeCell ref="G50:L50"/>
+    <mergeCell ref="A51:F51"/>
+    <mergeCell ref="G51:L51"/>
+    <mergeCell ref="A52:F52"/>
+    <mergeCell ref="G52:L52"/>
+    <mergeCell ref="A48:F48"/>
+    <mergeCell ref="G48:L48"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="G49:L49"/>
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="I18:L18"/>
+    <mergeCell ref="I19:L19"/>
+    <mergeCell ref="G22:L22"/>
+    <mergeCell ref="G21:L21"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:L20"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A18:F18"/>
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="G14:L14"/>
     <mergeCell ref="A5:F5"/>
@@ -3093,99 +3147,45 @@
     <mergeCell ref="G13:L13"/>
     <mergeCell ref="A13:F13"/>
     <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A15:F15"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="I18:L18"/>
-    <mergeCell ref="I19:L19"/>
-    <mergeCell ref="G22:L22"/>
-    <mergeCell ref="G21:L21"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:L20"/>
-    <mergeCell ref="A21:F21"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A20:F20"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="A50:F50"/>
-    <mergeCell ref="G50:L50"/>
-    <mergeCell ref="A51:F51"/>
-    <mergeCell ref="G51:L51"/>
-    <mergeCell ref="A52:F52"/>
-    <mergeCell ref="G52:L52"/>
-    <mergeCell ref="A48:F48"/>
-    <mergeCell ref="G48:L48"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="G49:L49"/>
-    <mergeCell ref="A56:F56"/>
-    <mergeCell ref="G56:L56"/>
-    <mergeCell ref="A57:F57"/>
-    <mergeCell ref="G57:L57"/>
-    <mergeCell ref="A58:F58"/>
-    <mergeCell ref="G58:L58"/>
-    <mergeCell ref="A53:F53"/>
-    <mergeCell ref="G53:L53"/>
-    <mergeCell ref="A54:F54"/>
-    <mergeCell ref="G54:L54"/>
-    <mergeCell ref="A55:F55"/>
-    <mergeCell ref="G55:L55"/>
-    <mergeCell ref="A62:F62"/>
-    <mergeCell ref="I62:L62"/>
-    <mergeCell ref="A63:F63"/>
-    <mergeCell ref="G63:I63"/>
-    <mergeCell ref="J63:L63"/>
-    <mergeCell ref="A59:F59"/>
-    <mergeCell ref="G59:L59"/>
-    <mergeCell ref="A60:F60"/>
-    <mergeCell ref="G60:L60"/>
-    <mergeCell ref="A61:F61"/>
-    <mergeCell ref="G61:H61"/>
-    <mergeCell ref="I61:L61"/>
-    <mergeCell ref="A67:C67"/>
-    <mergeCell ref="D67:F67"/>
-    <mergeCell ref="G67:L67"/>
-    <mergeCell ref="A68:F68"/>
-    <mergeCell ref="G68:L68"/>
-    <mergeCell ref="A64:F64"/>
-    <mergeCell ref="G64:L64"/>
-    <mergeCell ref="A65:F65"/>
-    <mergeCell ref="G65:L65"/>
-    <mergeCell ref="A66:F66"/>
-    <mergeCell ref="G66:L66"/>
-    <mergeCell ref="A72:F72"/>
-    <mergeCell ref="G72:L72"/>
-    <mergeCell ref="A73:F73"/>
-    <mergeCell ref="G73:L73"/>
-    <mergeCell ref="A74:F74"/>
-    <mergeCell ref="G74:L74"/>
-    <mergeCell ref="A69:F69"/>
-    <mergeCell ref="G69:L69"/>
-    <mergeCell ref="A70:F70"/>
-    <mergeCell ref="G70:L70"/>
-    <mergeCell ref="A71:F71"/>
-    <mergeCell ref="G71:L71"/>
-    <mergeCell ref="A78:F78"/>
-    <mergeCell ref="A79:F79"/>
-    <mergeCell ref="G79:H79"/>
-    <mergeCell ref="I79:L79"/>
-    <mergeCell ref="A75:F75"/>
-    <mergeCell ref="G75:L75"/>
-    <mergeCell ref="A76:F76"/>
-    <mergeCell ref="G76:L76"/>
-    <mergeCell ref="A77:F77"/>
-    <mergeCell ref="G78:L78"/>
-    <mergeCell ref="G77:L77"/>
-    <mergeCell ref="A82:F82"/>
-    <mergeCell ref="G82:L82"/>
-    <mergeCell ref="A83:F83"/>
-    <mergeCell ref="G83:L83"/>
-    <mergeCell ref="A80:F80"/>
-    <mergeCell ref="I80:L80"/>
-    <mergeCell ref="A81:F81"/>
-    <mergeCell ref="G81:I81"/>
-    <mergeCell ref="J81:L81"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="G23:L23"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="G24:L24"/>
+    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="G25:L25"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="G26:L26"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="G27:L27"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="G28:L28"/>
+    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="G29:L29"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="G30:L30"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="G31:L31"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="G32:L32"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="G33:L33"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="G34:L34"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="G35:L35"/>
+    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="I36:L36"/>
+    <mergeCell ref="A39:F39"/>
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="G39:L39"/>
+    <mergeCell ref="G40:L40"/>
+    <mergeCell ref="A37:F37"/>
+    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="I37:L37"/>
+    <mergeCell ref="G38:I38"/>
+    <mergeCell ref="J38:L38"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
